--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-FRM-13_ppq_oz_degerlendirme_ve_ppap_dosya_kontrol_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-FRM-13_ppq_oz_degerlendirme_ve_ppap_dosya_kontrol_listesi.xlsx
@@ -991,7 +991,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-13&amp;C&amp;"Arial,Regular"&amp;11PPQ Öz Değerlendirme ve PPAP Dosya Kontrol Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: PPQ/PPAP kontrolünün resmi kaynak ve sunum/saklama doğrulaması netleştirildi; yararlı kontrol maddeleri korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97a88117f3a74117"/>
   <x:tableParts count="1">
@@ -1509,7 +1510,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-13&amp;C&amp;"Arial,Regular"&amp;11PPQ Öz Değerlendirme ve PPAP Dosya Kontrol Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: PPQ/PPAP kontrolünün resmi kaynak ve sunum/saklama doğrulaması netleştirildi; yararlı kontrol maddeleri korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fed4c32755458f"/>
   <x:tableParts count="1">
@@ -1879,7 +1881,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-13&amp;C&amp;"Arial,Regular"&amp;11PPQ Öz Değerlendirme ve PPAP Dosya Kontrol Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: PPQ/PPAP kontrolünün resmi kaynak ve sunum/saklama doğrulaması netleştirildi; yararlı kontrol maddeleri korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe6031e56ae5437d"/>
   <x:tableParts count="1">
